--- a/Resource/test/测试Excel导出模板.xlsx
+++ b/Resource/test/测试Excel导出模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IdeaProjects\Rain平台\Resource\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47818990-8F1E-41BB-9D49-3605C8A767C9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496B641E-57DA-4BCB-84BD-9CCB99F62726}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,11 +51,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{one_begin:username}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{one_end:roleid}</t>
+    <t>{two_begin:username}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{two_end:roleid}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -418,6 +418,10 @@
     <col min="2" max="2" width="22.77734375" customWidth="1"/>
     <col min="3" max="3" width="29.88671875" customWidth="1"/>
     <col min="4" max="4" width="28.5546875" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
